--- a/downloads/korrigierte_referenz/Zoo_2NF.xlsx
+++ b/downloads/korrigierte_referenz/Zoo_2NF.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEHEGE_TIER" sheetId="1" r:id="R37f8985f05cd4c9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEHEGE" sheetId="2" r:id="R2d94d994d21141b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEHEGE_TIER" sheetId="1" r:id="Rea68bb6246a64afc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEHEGE" sheetId="2" r:id="R164d3a8672184abb"/>
   </x:sheets>
 </x:workbook>
 </file>
